--- a/backend/data/financials_by_company/1900.HK.xlsx
+++ b/backend/data/financials_by_company/1900.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,547 +644,610 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Restructuring And Mergern Acquisition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-10163408.902985</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.334896</v>
-      </c>
-      <c r="D2" t="n">
-        <v>172291000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-30348000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-30348000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22058000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>60778000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>514518000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>141943000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>81165000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1667000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10537000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8870000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>42242591.097015</v>
-      </c>
-      <c r="P2" t="n">
-        <v>22058000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>632493000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>1714186064</v>
+        <v>1654585567</v>
       </c>
       <c r="S2" t="n">
-        <v>1709061415</v>
+        <v>1654024868</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>22058000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22058000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>22058000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-24917000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>46975000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>46975000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>23653000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>70628000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-88906000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-36289000</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>36289000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1667000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>10537000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>8870000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>187294000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>117975000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>118887000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>118887000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>305269000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>514518000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>819787000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>819787000</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3019305.753957</v>
+        <v>1861096.861092</v>
       </c>
       <c r="C3" t="n">
-        <v>0.077861</v>
+        <v>0.084827</v>
       </c>
       <c r="D3" t="n">
-        <v>230373000</v>
+        <v>143040000</v>
       </c>
       <c r="E3" t="n">
-        <v>38778000</v>
+        <v>21940000</v>
       </c>
       <c r="F3" t="n">
-        <v>38778000</v>
+        <v>21940000</v>
       </c>
       <c r="G3" t="n">
-        <v>137197000</v>
+        <v>48490000</v>
       </c>
       <c r="H3" t="n">
-        <v>56776000</v>
+        <v>50603000</v>
       </c>
       <c r="I3" t="n">
-        <v>525710000</v>
+        <v>455161000</v>
       </c>
       <c r="J3" t="n">
-        <v>269151000</v>
+        <v>164980000</v>
       </c>
       <c r="K3" t="n">
-        <v>212375000</v>
+        <v>114377000</v>
       </c>
       <c r="L3" t="n">
-        <v>1917000</v>
+        <v>-5905000</v>
       </c>
       <c r="M3" t="n">
-        <v>9784000</v>
+        <v>11921000</v>
       </c>
       <c r="N3" t="n">
-        <v>11701000</v>
+        <v>6016000</v>
       </c>
       <c r="O3" t="n">
-        <v>101438305.753957</v>
+        <v>28411096.861092</v>
       </c>
       <c r="P3" t="n">
-        <v>137197000</v>
+        <v>48490000</v>
       </c>
       <c r="Q3" t="n">
-        <v>655608000</v>
+        <v>585126000</v>
       </c>
       <c r="R3" t="n">
-        <v>1690782170</v>
+        <v>1672933098</v>
       </c>
       <c r="S3" t="n">
-        <v>1686924102</v>
+        <v>1665090974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="V3" t="n">
-        <v>137197000</v>
+        <v>48490000</v>
       </c>
       <c r="W3" t="n">
-        <v>137197000</v>
+        <v>48490000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>137197000</v>
+        <v>48490000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-49620000</v>
+        <v>-45275000</v>
       </c>
       <c r="AA3" t="n">
-        <v>186817000</v>
+        <v>93765000</v>
       </c>
       <c r="AB3" t="n">
-        <v>186817000</v>
+        <v>93765000</v>
       </c>
       <c r="AC3" t="n">
-        <v>15774000</v>
+        <v>8691000</v>
       </c>
       <c r="AD3" t="n">
-        <v>202591000</v>
+        <v>102456000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-42688000</v>
+        <v>-50236000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-44708000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>21940000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-27740000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>44708000</v>
+        <v>5800000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1917000</v>
+        <v>-5905000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9784000</v>
+        <v>11921000</v>
       </c>
       <c r="AK3" t="n">
-        <v>11701000</v>
+        <v>6016000</v>
       </c>
       <c r="AL3" t="n">
-        <v>201787000</v>
+        <v>129298000</v>
       </c>
       <c r="AM3" t="n">
-        <v>129898000</v>
+        <v>129965000</v>
       </c>
       <c r="AN3" t="n">
-        <v>129914000</v>
+        <v>131275000</v>
       </c>
       <c r="AO3" t="n">
-        <v>129914000</v>
+        <v>131275000</v>
       </c>
       <c r="AP3" t="n">
-        <v>331685000</v>
+        <v>259263000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>525710000</v>
+        <v>455161000</v>
       </c>
       <c r="AR3" t="n">
-        <v>857395000</v>
+        <v>714424000</v>
       </c>
       <c r="AS3" t="n">
-        <v>857395000</v>
-      </c>
+        <v>714424000</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1861096.861092</v>
+        <v>3019305.753957</v>
       </c>
       <c r="C4" t="n">
-        <v>0.084827</v>
+        <v>0.077861</v>
       </c>
       <c r="D4" t="n">
-        <v>143040000</v>
+        <v>230373000</v>
       </c>
       <c r="E4" t="n">
-        <v>21940000</v>
+        <v>38778000</v>
       </c>
       <c r="F4" t="n">
-        <v>21940000</v>
+        <v>38778000</v>
       </c>
       <c r="G4" t="n">
-        <v>48490000</v>
+        <v>137197000</v>
       </c>
       <c r="H4" t="n">
-        <v>50603000</v>
+        <v>56776000</v>
       </c>
       <c r="I4" t="n">
-        <v>455161000</v>
+        <v>525710000</v>
       </c>
       <c r="J4" t="n">
-        <v>164980000</v>
+        <v>269151000</v>
       </c>
       <c r="K4" t="n">
-        <v>114377000</v>
+        <v>212375000</v>
       </c>
       <c r="L4" t="n">
-        <v>-5905000</v>
+        <v>1917000</v>
       </c>
       <c r="M4" t="n">
-        <v>11921000</v>
+        <v>9784000</v>
       </c>
       <c r="N4" t="n">
-        <v>6016000</v>
+        <v>11701000</v>
       </c>
       <c r="O4" t="n">
-        <v>28411096.861092</v>
+        <v>101438305.753957</v>
       </c>
       <c r="P4" t="n">
-        <v>48490000</v>
+        <v>137197000</v>
       </c>
       <c r="Q4" t="n">
-        <v>585126000</v>
+        <v>655608000</v>
       </c>
       <c r="R4" t="n">
-        <v>1672933098</v>
+        <v>1690782170</v>
       </c>
       <c r="S4" t="n">
-        <v>1665090974</v>
+        <v>1686924102</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="V4" t="n">
-        <v>48490000</v>
+        <v>137197000</v>
       </c>
       <c r="W4" t="n">
-        <v>48490000</v>
+        <v>137197000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>48490000</v>
+        <v>137197000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-45275000</v>
+        <v>-49620000</v>
       </c>
       <c r="AA4" t="n">
-        <v>93765000</v>
+        <v>186817000</v>
       </c>
       <c r="AB4" t="n">
-        <v>93765000</v>
+        <v>186817000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8691000</v>
+        <v>15774000</v>
       </c>
       <c r="AD4" t="n">
-        <v>102456000</v>
+        <v>202591000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-50236000</v>
+        <v>-42688000</v>
       </c>
       <c r="AF4" t="n">
-        <v>21940000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-27740000</v>
-      </c>
+        <v>-44708000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>5800000</v>
+        <v>44708000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5905000</v>
+        <v>1917000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11921000</v>
+        <v>9784000</v>
       </c>
       <c r="AK4" t="n">
-        <v>6016000</v>
+        <v>11701000</v>
       </c>
       <c r="AL4" t="n">
-        <v>129298000</v>
+        <v>201787000</v>
       </c>
       <c r="AM4" t="n">
-        <v>129965000</v>
+        <v>129898000</v>
       </c>
       <c r="AN4" t="n">
-        <v>131275000</v>
+        <v>129914000</v>
       </c>
       <c r="AO4" t="n">
-        <v>131275000</v>
+        <v>129914000</v>
       </c>
       <c r="AP4" t="n">
-        <v>259263000</v>
+        <v>331685000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>455161000</v>
+        <v>525710000</v>
       </c>
       <c r="AR4" t="n">
-        <v>714424000</v>
+        <v>857395000</v>
       </c>
       <c r="AS4" t="n">
-        <v>714424000</v>
-      </c>
+        <v>857395000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>4653036.955706</v>
+        <v>-10163408.902985</v>
       </c>
       <c r="C5" t="n">
-        <v>0.253696</v>
+        <v>0.334896</v>
       </c>
       <c r="D5" t="n">
-        <v>198384000</v>
+        <v>172291000</v>
       </c>
       <c r="E5" t="n">
-        <v>18341000</v>
+        <v>-30348000</v>
       </c>
       <c r="F5" t="n">
-        <v>18341000</v>
+        <v>-30348000</v>
       </c>
       <c r="G5" t="n">
-        <v>74519000</v>
+        <v>22058000</v>
       </c>
       <c r="H5" t="n">
-        <v>57519000</v>
+        <v>60778000</v>
       </c>
       <c r="I5" t="n">
-        <v>472970000</v>
+        <v>514518000</v>
       </c>
       <c r="J5" t="n">
-        <v>216725000</v>
+        <v>141943000</v>
       </c>
       <c r="K5" t="n">
-        <v>159206000</v>
+        <v>81165000</v>
       </c>
       <c r="L5" t="n">
-        <v>-11124000</v>
+        <v>-1667000</v>
       </c>
       <c r="M5" t="n">
-        <v>18037000</v>
+        <v>10537000</v>
       </c>
       <c r="N5" t="n">
-        <v>6913000</v>
+        <v>8870000</v>
       </c>
       <c r="O5" t="n">
-        <v>60831036.955706</v>
+        <v>42242591.097015</v>
       </c>
       <c r="P5" t="n">
-        <v>74519000</v>
+        <v>22058000</v>
       </c>
       <c r="Q5" t="n">
-        <v>620271000</v>
+        <v>632493000</v>
       </c>
       <c r="R5" t="n">
-        <v>1654585567</v>
+        <v>1714186064</v>
       </c>
       <c r="S5" t="n">
-        <v>1654024868</v>
+        <v>1709061415</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="V5" t="n">
-        <v>74519000</v>
+        <v>22058000</v>
       </c>
       <c r="W5" t="n">
-        <v>74519000</v>
+        <v>22058000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>74519000</v>
+        <v>22058000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-30836000</v>
+        <v>-24917000</v>
       </c>
       <c r="AA5" t="n">
-        <v>105355000</v>
+        <v>46975000</v>
       </c>
       <c r="AB5" t="n">
-        <v>105355000</v>
+        <v>46975000</v>
       </c>
       <c r="AC5" t="n">
-        <v>35814000</v>
+        <v>23653000</v>
       </c>
       <c r="AD5" t="n">
-        <v>141169000</v>
+        <v>70628000</v>
       </c>
       <c r="AE5" t="n">
-        <v>5284000</v>
+        <v>-88906000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-14158000</v>
+        <v>-36289000</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>14158000</v>
+        <v>36289000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-11124000</v>
+        <v>-1667000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18037000</v>
+        <v>10537000</v>
       </c>
       <c r="AK5" t="n">
-        <v>6913000</v>
+        <v>8870000</v>
       </c>
       <c r="AL5" t="n">
-        <v>120022000</v>
+        <v>187294000</v>
       </c>
       <c r="AM5" t="n">
-        <v>147301000</v>
+        <v>117975000</v>
       </c>
       <c r="AN5" t="n">
-        <v>148092000</v>
+        <v>118887000</v>
       </c>
       <c r="AO5" t="n">
-        <v>148092000</v>
+        <v>118887000</v>
       </c>
       <c r="AP5" t="n">
-        <v>267323000</v>
+        <v>305269000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>472970000</v>
+        <v>514518000</v>
       </c>
       <c r="AR5" t="n">
-        <v>740293000</v>
+        <v>819787000</v>
       </c>
       <c r="AS5" t="n">
-        <v>740293000</v>
+        <v>819787000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>312067.293529</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.048121</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-180680000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>379949000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6485000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>70488000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>66205000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>602698000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>199269000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>133064000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>626000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7465000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8091000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>437779067.293529</v>
+      </c>
+      <c r="P6" t="n">
+        <v>70488000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>790435000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>70488000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>70488000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>70488000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-49067000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>119555000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>119555000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6044000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>125599000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-26484000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-37108000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>13814000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>626000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>7465000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>8091000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>137414000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>187737000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>190393000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>190393000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>325151000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>602698000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>927849000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>927849000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-350170000</v>
       </c>
     </row>
   </sheetData>
@@ -1198,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL5"/>
+  <dimension ref="A1:BN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1517,761 +1580,867 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1720185862</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1720185862</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>246114000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1644796000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2127338000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>873926000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1644796000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1881224000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1881224000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2001124000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>119900000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1881224000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>7782000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>275112000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1041270000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>302000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>302000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>837170000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1165000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1165000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>836005000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>246114000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>246114000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>431991000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>39901000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>125788000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>266302000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2838294000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1128363000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>26289000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>70187000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>70187000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>284988000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>284988000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>68291000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>236428000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>118630000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>117798000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>468469000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-190272000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>658741000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3807000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>324594000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>17493000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>312847000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1709931000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>77590000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>241444000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>265926000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>265926000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>442948000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>12019000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>338487000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-129494000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>467981000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>331517000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1629000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>329888000</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>175687000</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1697691124</v>
+        <v>1675857996</v>
       </c>
       <c r="C3" t="n">
-        <v>1697691124</v>
+        <v>1675857996</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>275020000</v>
+        <v>258037000</v>
       </c>
       <c r="F3" t="n">
-        <v>1694439000</v>
+        <v>1549722000</v>
       </c>
       <c r="G3" t="n">
-        <v>2203206000</v>
+        <v>2037791000</v>
       </c>
       <c r="H3" t="n">
-        <v>930606000</v>
+        <v>865324000</v>
       </c>
       <c r="I3" t="n">
-        <v>1694439000</v>
+        <v>1549722000</v>
       </c>
       <c r="J3" t="n">
-        <v>1928186000</v>
+        <v>1779754000</v>
       </c>
       <c r="K3" t="n">
-        <v>1928186000</v>
+        <v>1779754000</v>
       </c>
       <c r="L3" t="n">
-        <v>2064759000</v>
+        <v>1895533000</v>
       </c>
       <c r="M3" t="n">
-        <v>136573000</v>
+        <v>115779000</v>
       </c>
       <c r="N3" t="n">
-        <v>1928186000</v>
+        <v>1779754000</v>
       </c>
       <c r="O3" t="n">
         <v>7782000</v>
       </c>
       <c r="P3" t="n">
-        <v>253054000</v>
+        <v>116817000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1073167000</v>
+        <v>1069770000</v>
       </c>
       <c r="R3" t="n">
-        <v>298000</v>
+        <v>294000</v>
       </c>
       <c r="S3" t="n">
-        <v>298000</v>
+        <v>294000</v>
       </c>
       <c r="T3" t="n">
-        <v>1033092000</v>
+        <v>945657000</v>
       </c>
       <c r="U3" t="n">
-        <v>4501000</v>
+        <v>1843000</v>
       </c>
       <c r="V3" t="n">
-        <v>4501000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+        <v>1843000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" t="n">
-        <v>1028591000</v>
+        <v>943814000</v>
       </c>
       <c r="Z3" t="n">
-        <v>275020000</v>
+        <v>258037000</v>
       </c>
       <c r="AA3" t="n">
-        <v>275020000</v>
+        <v>258037000</v>
       </c>
       <c r="AB3" t="n">
-        <v>565324000</v>
+        <v>452945000</v>
       </c>
       <c r="AC3" t="n">
-        <v>28682000</v>
+        <v>37813000</v>
       </c>
       <c r="AD3" t="n">
-        <v>101917000</v>
+        <v>106584000</v>
       </c>
       <c r="AE3" t="n">
-        <v>434725000</v>
+        <v>308548000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3097851000</v>
+        <v>2841190000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1138654000</v>
+        <v>1032052000</v>
       </c>
       <c r="AH3" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>158319000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>158319000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>55034000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55034000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>71150000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>230032000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>106273000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>123759000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>501617000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-136920000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>638537000</v>
+      </c>
+      <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="n">
-        <v>287593000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>287593000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>55960000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55960000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>68060000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>233747000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>115949000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>117798000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>493294000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-168976000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>662270000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>730000</v>
-      </c>
       <c r="AU3" t="n">
-        <v>322988000</v>
+        <v>294101000</v>
       </c>
       <c r="AV3" t="n">
-        <v>18816000</v>
+        <v>22043000</v>
       </c>
       <c r="AW3" t="n">
-        <v>319736000</v>
+        <v>322393000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1959197000</v>
+        <v>1809138000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>39818000</v>
+        <v>130183000</v>
       </c>
       <c r="BA3" t="n">
-        <v>266433000</v>
+        <v>265313000</v>
       </c>
       <c r="BB3" t="n">
-        <v>404218000</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>276384000</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
       <c r="BD3" t="n">
-        <v>404218000</v>
+        <v>276384000</v>
       </c>
       <c r="BE3" t="n">
-        <v>389700000</v>
+        <v>409938000</v>
       </c>
       <c r="BF3" t="n">
-        <v>15004000</v>
+        <v>15600000</v>
       </c>
       <c r="BG3" t="n">
-        <v>359467000</v>
+        <v>406007000</v>
       </c>
       <c r="BH3" t="n">
-        <v>-94672000</v>
+        <v>-73968000</v>
       </c>
       <c r="BI3" t="n">
-        <v>454139000</v>
+        <v>479975000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>484557000</v>
+        <v>305713000</v>
       </c>
       <c r="BK3" t="n">
-        <v>789000</v>
+        <v>10091000</v>
       </c>
       <c r="BL3" t="n">
-        <v>483768000</v>
-      </c>
+        <v>295622000</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1675857996</v>
+        <v>1697691124</v>
       </c>
       <c r="C4" t="n">
-        <v>1675857996</v>
+        <v>1697691124</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>258037000</v>
+        <v>275020000</v>
       </c>
       <c r="F4" t="n">
-        <v>1549722000</v>
+        <v>1694439000</v>
       </c>
       <c r="G4" t="n">
-        <v>2037791000</v>
+        <v>2203206000</v>
       </c>
       <c r="H4" t="n">
-        <v>865324000</v>
+        <v>930606000</v>
       </c>
       <c r="I4" t="n">
-        <v>1549722000</v>
+        <v>1694439000</v>
       </c>
       <c r="J4" t="n">
-        <v>1779754000</v>
+        <v>1928186000</v>
       </c>
       <c r="K4" t="n">
-        <v>1779754000</v>
+        <v>1928186000</v>
       </c>
       <c r="L4" t="n">
-        <v>1895533000</v>
+        <v>2064759000</v>
       </c>
       <c r="M4" t="n">
-        <v>115779000</v>
+        <v>136573000</v>
       </c>
       <c r="N4" t="n">
-        <v>1779754000</v>
+        <v>1928186000</v>
       </c>
       <c r="O4" t="n">
         <v>7782000</v>
       </c>
       <c r="P4" t="n">
-        <v>116817000</v>
+        <v>253054000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1069770000</v>
+        <v>1073167000</v>
       </c>
       <c r="R4" t="n">
-        <v>294000</v>
+        <v>298000</v>
       </c>
       <c r="S4" t="n">
-        <v>294000</v>
+        <v>298000</v>
       </c>
       <c r="T4" t="n">
-        <v>945657000</v>
+        <v>1033092000</v>
       </c>
       <c r="U4" t="n">
-        <v>1843000</v>
+        <v>4501000</v>
       </c>
       <c r="V4" t="n">
-        <v>1843000</v>
-      </c>
-      <c r="W4" t="n">
+        <v>4501000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>1028591000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>275020000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>275020000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>565324000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>28682000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>101917000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>434725000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3097851000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1138654000</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>943814000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>258037000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>258037000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>452945000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>37813000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>106584000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>308548000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2841190000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1032052000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15900000</v>
-      </c>
       <c r="AI4" t="n">
-        <v>158319000</v>
+        <v>287593000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>158319000</v>
+        <v>287593000</v>
       </c>
       <c r="AK4" t="n">
-        <v>55034000</v>
+        <v>55960000</v>
       </c>
       <c r="AL4" t="n">
-        <v>55034000</v>
+        <v>55960000</v>
       </c>
       <c r="AM4" t="n">
-        <v>71150000</v>
+        <v>68060000</v>
       </c>
       <c r="AN4" t="n">
-        <v>230032000</v>
+        <v>233747000</v>
       </c>
       <c r="AO4" t="n">
-        <v>106273000</v>
+        <v>115949000</v>
       </c>
       <c r="AP4" t="n">
-        <v>123759000</v>
+        <v>117798000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>501617000</v>
+        <v>493294000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-136920000</v>
+        <v>-168976000</v>
       </c>
       <c r="AS4" t="n">
-        <v>638537000</v>
+        <v>662270000</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>730000</v>
       </c>
       <c r="AU4" t="n">
-        <v>294101000</v>
+        <v>322988000</v>
       </c>
       <c r="AV4" t="n">
-        <v>22043000</v>
+        <v>18816000</v>
       </c>
       <c r="AW4" t="n">
-        <v>322393000</v>
+        <v>319736000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1809138000</v>
+        <v>1959197000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>130183000</v>
+        <v>39818000</v>
       </c>
       <c r="BA4" t="n">
-        <v>265313000</v>
+        <v>266433000</v>
       </c>
       <c r="BB4" t="n">
-        <v>276384000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
+        <v>404218000</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>276384000</v>
+        <v>404218000</v>
       </c>
       <c r="BE4" t="n">
-        <v>409938000</v>
+        <v>389700000</v>
       </c>
       <c r="BF4" t="n">
-        <v>15600000</v>
+        <v>15004000</v>
       </c>
       <c r="BG4" t="n">
-        <v>406007000</v>
+        <v>359467000</v>
       </c>
       <c r="BH4" t="n">
-        <v>-73968000</v>
+        <v>-94672000</v>
       </c>
       <c r="BI4" t="n">
-        <v>479975000</v>
+        <v>454139000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>305713000</v>
+        <v>484557000</v>
       </c>
       <c r="BK4" t="n">
-        <v>10091000</v>
+        <v>789000</v>
       </c>
       <c r="BL4" t="n">
-        <v>295622000</v>
-      </c>
+        <v>483768000</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1654024868</v>
+        <v>1720185862</v>
       </c>
       <c r="C5" t="n">
-        <v>1654024868</v>
-      </c>
-      <c r="D5" t="n">
-        <v>26289000</v>
-      </c>
+        <v>1720185862</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>344158000</v>
+        <v>246114000</v>
       </c>
       <c r="F5" t="n">
-        <v>1624405000</v>
+        <v>1644796000</v>
       </c>
       <c r="G5" t="n">
-        <v>2116872000</v>
+        <v>2127338000</v>
       </c>
       <c r="H5" t="n">
-        <v>900080000</v>
+        <v>873926000</v>
       </c>
       <c r="I5" t="n">
-        <v>1624405000</v>
+        <v>1644796000</v>
       </c>
       <c r="J5" t="n">
-        <v>1772714000</v>
+        <v>1881224000</v>
       </c>
       <c r="K5" t="n">
-        <v>1807714000</v>
+        <v>1881224000</v>
       </c>
       <c r="L5" t="n">
-        <v>1854446000</v>
+        <v>2001124000</v>
       </c>
       <c r="M5" t="n">
-        <v>81732000</v>
+        <v>119900000</v>
       </c>
       <c r="N5" t="n">
-        <v>1772714000</v>
+        <v>1881224000</v>
       </c>
       <c r="O5" t="n">
         <v>7782000</v>
       </c>
       <c r="P5" t="n">
-        <v>22900000</v>
+        <v>275112000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1088725000</v>
+        <v>1041270000</v>
       </c>
       <c r="R5" t="n">
-        <v>290000</v>
+        <v>302000</v>
       </c>
       <c r="S5" t="n">
-        <v>290000</v>
+        <v>302000</v>
       </c>
       <c r="T5" t="n">
-        <v>1201143000</v>
+        <v>837170000</v>
       </c>
       <c r="U5" t="n">
-        <v>44363000</v>
+        <v>1165000</v>
       </c>
       <c r="V5" t="n">
-        <v>9363000</v>
+        <v>1165000</v>
       </c>
       <c r="W5" t="n">
-        <v>35000000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>35000000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1156780000</v>
+        <v>836005000</v>
       </c>
       <c r="Z5" t="n">
-        <v>309158000</v>
+        <v>246114000</v>
       </c>
       <c r="AA5" t="n">
-        <v>309158000</v>
+        <v>246114000</v>
       </c>
       <c r="AB5" t="n">
-        <v>470921000</v>
+        <v>431991000</v>
       </c>
       <c r="AC5" t="n">
-        <v>29856000</v>
+        <v>39901000</v>
       </c>
       <c r="AD5" t="n">
-        <v>132744000</v>
+        <v>125788000</v>
       </c>
       <c r="AE5" t="n">
-        <v>308321000</v>
+        <v>266302000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3055589000</v>
+        <v>2838294000</v>
       </c>
       <c r="AG5" t="n">
-        <v>998729000</v>
+        <v>1128363000</v>
       </c>
       <c r="AH5" t="n">
-        <v>720000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>193102000</v>
+        <v>70187000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>193102000</v>
+        <v>70187000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000000</v>
+        <v>284988000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000000</v>
+        <v>284988000</v>
       </c>
       <c r="AM5" t="n">
-        <v>92252000</v>
+        <v>68291000</v>
       </c>
       <c r="AN5" t="n">
-        <v>148309000</v>
+        <v>236428000</v>
       </c>
       <c r="AO5" t="n">
-        <v>24550000</v>
+        <v>118630000</v>
       </c>
       <c r="AP5" t="n">
-        <v>123759000</v>
+        <v>117798000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>533346000</v>
+        <v>468469000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-106526000</v>
+        <v>-190272000</v>
       </c>
       <c r="AS5" t="n">
-        <v>639872000</v>
+        <v>658741000</v>
       </c>
       <c r="AT5" t="n">
-        <v>24164000</v>
+        <v>3807000</v>
       </c>
       <c r="AU5" t="n">
-        <v>263602000</v>
+        <v>324594000</v>
       </c>
       <c r="AV5" t="n">
-        <v>28240000</v>
+        <v>17493000</v>
       </c>
       <c r="AW5" t="n">
-        <v>323866000</v>
+        <v>312847000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>2056860000</v>
+        <v>1709931000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>30269000</v>
+        <v>77590000</v>
       </c>
       <c r="BA5" t="n">
-        <v>274022000</v>
+        <v>241444000</v>
       </c>
       <c r="BB5" t="n">
-        <v>405007000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>175687000</v>
-      </c>
+        <v>265926000</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>229320000</v>
+        <v>265926000</v>
       </c>
       <c r="BE5" t="n">
-        <v>464476000</v>
+        <v>442948000</v>
       </c>
       <c r="BF5" t="n">
-        <v>15600000</v>
+        <v>12019000</v>
       </c>
       <c r="BG5" t="n">
-        <v>549607000</v>
+        <v>338487000</v>
       </c>
       <c r="BH5" t="n">
-        <v>-75496000</v>
+        <v>-129494000</v>
       </c>
       <c r="BI5" t="n">
-        <v>625103000</v>
+        <v>467981000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>317879000</v>
+        <v>331517000</v>
       </c>
       <c r="BK5" t="n">
-        <v>10000</v>
+        <v>1629000</v>
       </c>
       <c r="BL5" t="n">
-        <v>317869000</v>
+        <v>329888000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>329888000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1720185862</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1720185862</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>283468000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1518400000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2110726000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1207249000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1518400000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1827258000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1842545000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2242285000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>415027000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1827258000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7782000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>158955000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1041270000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>302000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>302000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>998094000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>21693000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6406000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>15287000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>15287000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>976401000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>268181000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>268181000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>427666000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>49119000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>124572000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>253975000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3240379000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1056729000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1154000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>78101000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>78101000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>218130000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>218130000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>55879000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>308858000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>128059000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>180799000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>384807000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-99789000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>484596000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>39670000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>156356000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>26871000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>261699000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2183650000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>39682000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>174086000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>402703000</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>402703000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>285103000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>12019000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>467303000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-148518000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>615821000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>802754000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>103319000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>699435000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>699435000</v>
       </c>
     </row>
   </sheetData>
@@ -2285,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2544,595 +2713,697 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Other Cash Adjustment Outside Changein Cash</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Sale Of PPE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-31769000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-264700000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>235535000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-7830000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>329888000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>483768000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2010000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-155890000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-83126000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1361000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-35526000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-35526000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-29165000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-29165000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-264700000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>235535000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>-48825000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2413000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>12851000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>20261000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-7410000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-56259000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-56259000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-7830000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-7830000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-23939000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>7007000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8870000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-10537000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-206746000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-104586000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-168368000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>22219000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>138292000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-94303000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1667000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>442000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>60778000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>22574000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>38204000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-22419000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>29867000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>-281753000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-515652000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>233899000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>70628000</v>
-      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>221295000</v>
+        <v>23855000</v>
       </c>
       <c r="C3" t="n">
-        <v>-220152000</v>
+        <v>-219975000</v>
       </c>
       <c r="D3" t="n">
-        <v>240949000</v>
+        <v>198221000</v>
       </c>
       <c r="E3" t="n">
-        <v>-7424000</v>
+        <v>-39884000</v>
       </c>
       <c r="F3" t="n">
-        <v>483768000</v>
+        <v>295622000</v>
       </c>
       <c r="G3" t="n">
-        <v>295622000</v>
+        <v>317869000</v>
       </c>
       <c r="H3" t="n">
-        <v>2089000</v>
+        <v>-2076000</v>
       </c>
       <c r="I3" t="n">
-        <v>186057000</v>
+        <v>-20171000</v>
       </c>
       <c r="J3" t="n">
-        <v>-12550000</v>
+        <v>-19835000</v>
       </c>
       <c r="K3" t="n">
-        <v>1304000</v>
+        <v>1919000</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>-21754000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>-21754000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-219975000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>198221000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-64075000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1518000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-45690000</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>20797000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>20797000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-220152000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>240949000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>20797000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-220152000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>240949000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-30112000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1871000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-51645000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>24875000</v>
-      </c>
       <c r="Y3" t="n">
-        <v>-76520000</v>
+        <v>-45690000</v>
       </c>
       <c r="Z3" t="n">
-        <v>27086000</v>
+        <v>19981000</v>
       </c>
       <c r="AA3" t="n">
-        <v>37479000</v>
+        <v>19981000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-10393000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="n">
-        <v>-7424000</v>
+        <v>-39884000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-7424000</v>
+        <v>-39884000</v>
       </c>
       <c r="AG3" t="n">
-        <v>228719000</v>
+        <v>63739000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-13609000</v>
+        <v>-12878000</v>
       </c>
       <c r="AI3" t="n">
-        <v>11701000</v>
+        <v>6016000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-9784000</v>
+        <v>-11921000</v>
       </c>
       <c r="AK3" t="n">
-        <v>500000</v>
+        <v>-17500000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-6460000</v>
+        <v>-166476000</v>
       </c>
       <c r="AM3" t="n">
-        <v>118450000</v>
+        <v>34304000</v>
       </c>
       <c r="AN3" t="n">
-        <v>21957000</v>
+        <v>-120492000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-127834000</v>
+        <v>-47262000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-5613000</v>
+        <v>282426000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1917000</v>
+        <v>3057000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1564000</v>
+        <v>3995000</v>
       </c>
       <c r="AS3" t="n">
-        <v>56776000</v>
+        <v>50603000</v>
       </c>
       <c r="AT3" t="n">
-        <v>18818000</v>
+        <v>10007000</v>
       </c>
       <c r="AU3" t="n">
-        <v>37958000</v>
+        <v>40596000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2649000</v>
+        <v>-91730000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-70771000</v>
+        <v>52559000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-27740000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>202591000</v>
-      </c>
+        <v>102456000</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>23855000</v>
+        <v>221295000</v>
       </c>
       <c r="C4" t="n">
-        <v>-219975000</v>
+        <v>-220152000</v>
       </c>
       <c r="D4" t="n">
-        <v>198221000</v>
+        <v>240949000</v>
       </c>
       <c r="E4" t="n">
-        <v>-39884000</v>
+        <v>-7424000</v>
       </c>
       <c r="F4" t="n">
+        <v>483768000</v>
+      </c>
+      <c r="G4" t="n">
         <v>295622000</v>
       </c>
-      <c r="G4" t="n">
-        <v>317869000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-2076000</v>
+        <v>2089000</v>
       </c>
       <c r="I4" t="n">
-        <v>-20171000</v>
+        <v>186057000</v>
       </c>
       <c r="J4" t="n">
-        <v>-19835000</v>
+        <v>-12550000</v>
       </c>
       <c r="K4" t="n">
-        <v>1919000</v>
+        <v>1304000</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>-21754000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>20797000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20797000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-220152000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>240949000</v>
+      </c>
       <c r="R4" t="n">
-        <v>-21754000</v>
+        <v>20797000</v>
       </c>
       <c r="S4" t="n">
-        <v>-219975000</v>
+        <v>-220152000</v>
       </c>
       <c r="T4" t="n">
-        <v>198221000</v>
+        <v>240949000</v>
       </c>
       <c r="U4" t="n">
-        <v>-64075000</v>
+        <v>-30112000</v>
       </c>
       <c r="V4" t="n">
-        <v>1518000</v>
+        <v>1871000</v>
       </c>
       <c r="W4" t="n">
-        <v>-45690000</v>
+        <v>-51645000</v>
       </c>
       <c r="X4" t="n">
+        <v>24875000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-76520000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>27086000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>37479000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-10393000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>-7424000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-7424000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>228719000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-13609000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>11701000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-9784000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-6460000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>118450000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21957000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-127834000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-5613000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1917000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1564000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>56776000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>18818000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>37958000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-2649000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-70771000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="AY4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="n">
-        <v>-45690000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>19981000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>19981000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-39884000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-39884000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>63739000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-12878000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6016000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-11921000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-17500000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-166476000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>34304000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-120492000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-47262000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>282426000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3057000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3995000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>50603000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10007000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>40596000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-91730000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>52559000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-27740000</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>102456000</v>
-      </c>
+        <v>202591000</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>327664000</v>
+        <v>-31769000</v>
       </c>
       <c r="C5" t="n">
-        <v>-515652000</v>
+        <v>-264700000</v>
       </c>
       <c r="D5" t="n">
-        <v>233899000</v>
+        <v>235535000</v>
       </c>
       <c r="E5" t="n">
-        <v>-60783000</v>
+        <v>-7830000</v>
       </c>
       <c r="F5" t="n">
-        <v>317869000</v>
+        <v>329888000</v>
       </c>
       <c r="G5" t="n">
-        <v>240622000</v>
+        <v>483768000</v>
       </c>
       <c r="H5" t="n">
-        <v>11745000</v>
+        <v>2010000</v>
       </c>
       <c r="I5" t="n">
-        <v>65502000</v>
+        <v>-155890000</v>
       </c>
       <c r="J5" t="n">
-        <v>-281753000</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>-83126000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1361000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-35526000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-35526000</v>
+      </c>
       <c r="N5" t="n">
-        <v>-281753000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>-281753000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-515652000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>233899000</v>
-      </c>
+        <v>-29165000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-29165000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-264700000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>235535000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-41192000</v>
+        <v>-48825000</v>
       </c>
       <c r="V5" t="n">
-        <v>2789000</v>
+        <v>2413000</v>
       </c>
       <c r="W5" t="n">
-        <v>16802000</v>
+        <v>12851000</v>
       </c>
       <c r="X5" t="n">
-        <v>19099000</v>
+        <v>20261000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2297000</v>
+        <v>-7410000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-56259000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>-56259000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-60777000</v>
+        <v>-7830000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-60777000</v>
+        <v>-7830000</v>
       </c>
       <c r="AG5" t="n">
-        <v>388447000</v>
+        <v>-23939000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-13880000</v>
+        <v>7007000</v>
       </c>
       <c r="AI5" t="n">
-        <v>11423000</v>
+        <v>8870000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-18037000</v>
+        <v>-10537000</v>
       </c>
       <c r="AK5" t="n">
-        <v>220481000</v>
+        <v>-206746000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-45945000</v>
+        <v>-37772000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2839000</v>
+        <v>-235182000</v>
       </c>
       <c r="AN5" t="n">
-        <v>26009000</v>
+        <v>22219000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-46526000</v>
+        <v>138292000</v>
       </c>
       <c r="AP5" t="n">
-        <v>284104000</v>
+        <v>-94303000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5267000</v>
+        <v>1667000</v>
       </c>
       <c r="AR5" t="n">
-        <v>232000</v>
+        <v>442000</v>
       </c>
       <c r="AS5" t="n">
-        <v>57519000</v>
+        <v>60778000</v>
       </c>
       <c r="AT5" t="n">
-        <v>6729000</v>
+        <v>22574000</v>
       </c>
       <c r="AU5" t="n">
-        <v>50790000</v>
+        <v>38204000</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-22419000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-34548000</v>
+        <v>29867000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>3629000</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>141169000</v>
+        <v>70628000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>231838000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-236006000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>273466000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-51540000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>699435000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>329888000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2566000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>391704000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-3886000</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37460000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>37460000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-236006000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>273466000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>112212000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>169799000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>583373000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-413574000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-10059000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>70020000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-80079000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-151000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-151000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-51377000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-51389000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>283378000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-41644000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8091000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-7465000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>97021000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>37908000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5044000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>90791000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-110027000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>73305000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-350796000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4451000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>66205000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>26388000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>39817000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-6295000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-26423000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>189000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>125599000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-24723000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12000</v>
       </c>
     </row>
   </sheetData>
@@ -3672,74 +3943,74 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
       <c r="DO1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
@@ -3747,112 +4018,112 @@
       </c>
       <c r="DP1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3877,10 +4148,8 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100015</t>
-        </is>
+      <c r="D2" t="n">
+        <v>100015</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3937,7 +4206,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jie  Liao', 'age': 59, 'title': 'Executive Chairman', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 1737662, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hailin  Jiang', 'age': 57, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 2459371, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Haibin  Luo', 'age': 49, 'title': 'President', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yi  Mou', 'age': 58, 'title': 'CFO &amp; GM of Financial Management Department', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 52130, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming Shu  Leung FCCA, FCPA', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 406613, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jie  Liao', 'age': 59, 'title': 'Executive Chairman', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 1737388, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hailin  Jiang', 'age': 57, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 2458984, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Haibin  Luo', 'age': 49, 'title': 'President', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yi  Mou', 'age': 58, 'title': 'CFO &amp; GM of Financial Management Department', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 52122, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming Shu  Leung FCCA, FCPA', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 406549, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3955,28 +4224,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.26</v>
+        <v>0.248</v>
       </c>
       <c r="V2" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="W2" t="n">
-        <v>0.26</v>
+        <v>0.226</v>
       </c>
       <c r="X2" t="n">
-        <v>0.26</v>
+        <v>0.248</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.26</v>
+        <v>0.248</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.26</v>
+        <v>0.226</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.26</v>
+        <v>0.248</v>
       </c>
       <c r="AC2" t="n">
         <v>1723680000</v>
@@ -3985,31 +4254,31 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="AF2" t="n">
-        <v>5.2</v>
+        <v>4.7999997</v>
       </c>
       <c r="AG2" t="n">
-        <v>3000</v>
+        <v>35000</v>
       </c>
       <c r="AH2" t="n">
-        <v>3000</v>
+        <v>35000</v>
       </c>
       <c r="AI2" t="n">
-        <v>480583</v>
+        <v>459050</v>
       </c>
       <c r="AJ2" t="n">
-        <v>162100</v>
+        <v>179200</v>
       </c>
       <c r="AK2" t="n">
-        <v>162100</v>
+        <v>179200</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.25</v>
+        <v>0.228</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.26</v>
+        <v>0.246</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4018,13 +4287,13 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>447248320</v>
+        <v>412844608</v>
       </c>
       <c r="AQ2" t="n">
-        <v>428326279</v>
+        <v>412844606</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.145</v>
+        <v>0.185</v>
       </c>
       <c r="AS2" t="n">
         <v>0.44</v>
@@ -4036,13 +4305,13 @@
         <v>0.105</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.48202705</v>
+        <v>0.44494805</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.25422</v>
+        <v>0.24796</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2833</v>
+        <v>0.28343</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4059,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>342989312</v>
+        <v>325787456</v>
       </c>
       <c r="BD2" t="n">
         <v>0.07597</v>
@@ -4080,10 +4349,10 @@
         <v>1720185862</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.2300622</v>
+        <v>1.2300708</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.2113714</v>
+        <v>0.19511071</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4104,16 +4373,16 @@
         <v>0.34</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.37</v>
+        <v>0.351</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.853</v>
+        <v>1.76</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.6774192999999999</v>
+        <v>0.182266</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.0227</v>
@@ -4127,7 +4396,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4226,140 +4495,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DA2" t="n">
+        <v>-3.2258072</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>CHINA ITS</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>China ITS (Holdings) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>1780452348</v>
-      </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DG2" t="n">
+        <v>1781752206</v>
+      </c>
+      <c r="DH2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>finmb_83912834</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DG2" t="n">
+      <c r="DL2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DI2" t="b">
+      <c r="DN2" t="b">
         <v>0</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>CHINA ITS</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>China ITS (Holdings) Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.26</v>
       </c>
       <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1279157400000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.008000001</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.226 - 0.248</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DQ2" t="n">
-        <v>480583</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.114999995</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.79310346</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>0.145 - 0.44</t>
-        </is>
-      </c>
       <c r="DU2" t="n">
-        <v>-0.18</v>
+        <v>459050</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.40909094</v>
+        <v>0.054999992</v>
       </c>
       <c r="DW2" t="n">
-        <v>67.74193</v>
-      </c>
-      <c r="DX2" t="n">
+        <v>0.29729724</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>0.185 - 0.44</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.45454547</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>18.2266</v>
+      </c>
+      <c r="EB2" t="n">
         <v>1743432810</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EC2" t="n">
         <v>1743432810</v>
       </c>
-      <c r="DZ2" t="b">
+      <c r="ED2" t="b">
         <v>0</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EE2" t="n">
         <v>0.05</v>
       </c>
-      <c r="EB2" t="n">
-        <v>0.0057799816</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.02273614</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.023300022</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.082245044</v>
-      </c>
       <c r="EF2" t="n">
+        <v>-0.007960007</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.032101978</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.043430015</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.15323013</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EK2" t="n">
         <v>15</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1279157400000</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>0.26 - 0.26</t>
-        </is>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
